--- a/seeds/staff/staff-list.xlsx
+++ b/seeds/staff/staff-list.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="120">
   <si>
     <t>S/N</t>
   </si>
@@ -181,7 +181,7 @@
     <t>Cynthia Osasere Osakunih</t>
   </si>
   <si>
-    <t>Operations&amp; People Lead</t>
+    <t>Operations &amp; People Lead</t>
   </si>
   <si>
     <t>HR &amp; Operations</t>
@@ -250,7 +250,7 @@
     <t>Gideon Fidelis Ekom</t>
   </si>
   <si>
-    <t>Markerting &amp; Growth Officer - Enugu</t>
+    <t>Marketing &amp; Growth Officer - Enugu</t>
   </si>
   <si>
     <t>gideonfidelisekom@gmail.com</t>
@@ -262,7 +262,7 @@
     <t>Adaeze Chike</t>
   </si>
   <si>
-    <t>Markerting &amp; Growth Officer - Abia</t>
+    <t>Marketing &amp; Growth Officer - Abia</t>
   </si>
   <si>
     <t>adaezechike@gmail.com</t>
@@ -274,10 +274,10 @@
     <t>Chinyere Elechi</t>
   </si>
   <si>
-    <t>Head PR, Markerting &amp; Brand Strategy</t>
-  </si>
-  <si>
-    <t>chinyereelechi@gheil.com</t>
+    <t>Head PR, Marketing &amp; Brand Strategy</t>
+  </si>
+  <si>
+    <t>chinyereelechi@gmail.com</t>
   </si>
   <si>
     <t>Hybrid</t>
@@ -292,7 +292,7 @@
     <t>PR &amp; Marketing Lead - MyLagosApp</t>
   </si>
   <si>
-    <t>davididowuagida@gpril.com</t>
+    <t>davididowuagida@gmail.com</t>
   </si>
   <si>
     <t>00029</t>
@@ -1181,7 +1181,7 @@
         <v>62</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>35</v>
@@ -1642,7 +1642,9 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="7"/>
+      <c r="I20" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7" t="s">
@@ -1675,7 +1677,9 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="7"/>
+      <c r="I21" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7" t="s">
